--- a/03_Outputs/all/03_DS/ds_idx7_gini.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx7_gini.xlsx
@@ -388,10 +388,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.5278040650204081</v>
+        <v>0.5278040650204077</v>
       </c>
       <c r="D2">
-        <v>0.2654822591679183</v>
+        <v>0.2654822591679162</v>
       </c>
     </row>
     <row r="3">
@@ -409,7 +409,7 @@
         <v>-1.542092852015935</v>
       </c>
       <c r="D3">
-        <v>0.3408577808688997</v>
+        <v>0.340857780868899</v>
       </c>
     </row>
     <row r="4">
@@ -424,10 +424,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.824746544734146</v>
+        <v>1.824746544734147</v>
       </c>
       <c r="D4">
-        <v>1.096305705775367</v>
+        <v>1.096305705775365</v>
       </c>
     </row>
     <row r="5">
@@ -442,10 +442,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.1761495105165484</v>
+        <v>-0.1761495105165489</v>
       </c>
       <c r="D5">
-        <v>0.2600216268651019</v>
+        <v>0.2600216268651003</v>
       </c>
     </row>
     <row r="6">
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.6028369461790604</v>
+        <v>-0.6028369461790613</v>
       </c>
       <c r="D6">
-        <v>-0.1569859244377418</v>
+        <v>-0.1569859244377431</v>
       </c>
     </row>
     <row r="7">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>-1.369012715595934</v>
+        <v>-1.369012715595935</v>
       </c>
       <c r="D7">
-        <v>-0.01844647479004568</v>
+        <v>-0.01844647479004657</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         <v>-1.068207148411658</v>
       </c>
       <c r="D8">
-        <v>0.5603283531523392</v>
+        <v>0.560328353152338</v>
       </c>
     </row>
     <row r="9">
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-1.440189838704748</v>
+        <v>-1.440189838704749</v>
       </c>
       <c r="D9">
-        <v>-0.1988865518566022</v>
+        <v>-0.1988865518566031</v>
       </c>
     </row>
     <row r="10">
@@ -535,7 +535,7 @@
         <v>4.03703149997489</v>
       </c>
       <c r="D10">
-        <v>0.2532755037185319</v>
+        <v>0.2532755037185275</v>
       </c>
     </row>
     <row r="11">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.002055211761196876</v>
+        <v>-0.002055211761197384</v>
       </c>
       <c r="D11">
-        <v>0.2857464767100708</v>
+        <v>0.285746476710069</v>
       </c>
     </row>
     <row r="12">
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.8098151428033303</v>
+        <v>0.8098151428033292</v>
       </c>
       <c r="D12">
-        <v>-0.4780946104473875</v>
+        <v>-0.4780946104473899</v>
       </c>
     </row>
     <row r="13">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.6924743090411227</v>
+        <v>0.6924743090411217</v>
       </c>
       <c r="D13">
-        <v>-0.4494542449617657</v>
+        <v>-0.4494542449617679</v>
       </c>
     </row>
     <row r="14">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.5010880452027421</v>
+        <v>-0.5010880452027427</v>
       </c>
       <c r="D14">
-        <v>0.1217045001661096</v>
+        <v>0.1217045001661081</v>
       </c>
     </row>
     <row r="15">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.03456850974877896</v>
+        <v>-0.03456850974878023</v>
       </c>
       <c r="D15">
-        <v>-0.6915345140713404</v>
+        <v>-0.6915345140713421</v>
       </c>
     </row>
     <row r="16">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.5504573899894128</v>
+        <v>0.5504573899894123</v>
       </c>
       <c r="D16">
-        <v>0.2163427167690039</v>
+        <v>0.2163427167690018</v>
       </c>
     </row>
     <row r="17">
@@ -661,7 +661,7 @@
         <v>-1.224326851267169</v>
       </c>
       <c r="D17">
-        <v>0.4450048957241042</v>
+        <v>0.445004895724103</v>
       </c>
     </row>
     <row r="18">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>-1.002896553013608</v>
+        <v>-1.002896553013609</v>
       </c>
       <c r="D18">
-        <v>-0.01670578261179575</v>
+        <v>-0.016705782611797</v>
       </c>
     </row>
     <row r="19">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.2794202951739806</v>
+        <v>-0.2794202951739814</v>
       </c>
       <c r="D19">
-        <v>-0.06315920267783622</v>
+        <v>-0.06315920267783787</v>
       </c>
     </row>
     <row r="20">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.2784063424160874</v>
+        <v>-0.278406342416088</v>
       </c>
       <c r="D20">
-        <v>0.2517648114262103</v>
+        <v>0.2517648114262087</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>-1.700516527892655</v>
+        <v>-1.700516527892656</v>
       </c>
       <c r="D21">
-        <v>0.1869534224381617</v>
+        <v>0.186953422438161</v>
       </c>
     </row>
     <row r="22">
@@ -748,10 +748,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.8863233939218845</v>
+        <v>-0.8863233939218852</v>
       </c>
       <c r="D22">
-        <v>0.12111639601242</v>
+        <v>0.1211163960124187</v>
       </c>
     </row>
     <row r="23">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>-1.946808841116448</v>
+        <v>-1.946808841116449</v>
       </c>
       <c r="D23">
-        <v>0.6430634851478272</v>
+        <v>0.6430634851478267</v>
       </c>
     </row>
     <row r="24">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.935253019484016</v>
+        <v>0.9352530194840152</v>
       </c>
       <c r="D24">
-        <v>-0.09524708645691782</v>
+        <v>-0.09524708645692015</v>
       </c>
     </row>
     <row r="25">
@@ -805,7 +805,7 @@
         <v>-2.046364887237699</v>
       </c>
       <c r="D25">
-        <v>0.6822195673756281</v>
+        <v>0.6822195673756275</v>
       </c>
     </row>
     <row r="26">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.1138114154709965</v>
+        <v>0.1138114154709958</v>
       </c>
       <c r="D26">
-        <v>-0.01250719407634277</v>
+        <v>-0.01250719407634461</v>
       </c>
     </row>
     <row r="27">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.8933275873803103</v>
+        <v>0.8933275873803087</v>
       </c>
       <c r="D27">
-        <v>-0.9200948810240939</v>
+        <v>-0.9200948810240962</v>
       </c>
     </row>
     <row r="28">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.7192890037283696</v>
+        <v>0.7192890037283685</v>
       </c>
       <c r="D28">
-        <v>-0.5187252248790973</v>
+        <v>-0.5187252248790996</v>
       </c>
     </row>
     <row r="29">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.9554609679821621</v>
+        <v>0.9554609679821615</v>
       </c>
       <c r="D29">
-        <v>0.1900138881219063</v>
+        <v>0.190013888121904</v>
       </c>
     </row>
     <row r="30">
@@ -895,7 +895,7 @@
         <v>-1.161431395805959</v>
       </c>
       <c r="D30">
-        <v>-0.2571578833161526</v>
+        <v>-0.2571578833161537</v>
       </c>
     </row>
     <row r="31">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.5271820179360895</v>
+        <v>-0.5271820179360905</v>
       </c>
       <c r="D31">
-        <v>-0.3550583343673439</v>
+        <v>-0.3550583343673454</v>
       </c>
     </row>
     <row r="32">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.4064512345848008</v>
+        <v>-0.4064512345848017</v>
       </c>
       <c r="D32">
-        <v>-0.1712308495467894</v>
+        <v>-0.1712308495467909</v>
       </c>
     </row>
     <row r="33">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.7771068926971052</v>
+        <v>0.7771068926971045</v>
       </c>
       <c r="D33">
-        <v>-0.03201342311755771</v>
+        <v>-0.03201342311756</v>
       </c>
     </row>
     <row r="34">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>-2.314668138882454</v>
+        <v>-2.314668138882455</v>
       </c>
       <c r="D34">
-        <v>-0.2468293223154241</v>
+        <v>-0.2468293223154243</v>
       </c>
     </row>
     <row r="35">
@@ -985,7 +985,7 @@
         <v>1.501143190473957</v>
       </c>
       <c r="D35">
-        <v>-0.02943696918240285</v>
+        <v>-0.02943696918240557</v>
       </c>
     </row>
     <row r="36">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.2019641352629647</v>
+        <v>-0.201964135262965</v>
       </c>
       <c r="D36">
-        <v>0.505186040935643</v>
+        <v>0.5051860409356413</v>
       </c>
     </row>
     <row r="37">
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.2831127784408239</v>
+        <v>-0.2831127784408247</v>
       </c>
       <c r="D37">
-        <v>-0.004367366077560633</v>
+        <v>-0.004367366077562246</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>-2.14914707843281</v>
+        <v>-2.149147078432811</v>
       </c>
       <c r="D38">
-        <v>0.1060264840916163</v>
+        <v>0.1060264840916161</v>
       </c>
     </row>
     <row r="39">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="C39">
-        <v>3.444750356678856</v>
+        <v>3.444750356678857</v>
       </c>
       <c r="D39">
-        <v>1.248633125233325</v>
+        <v>1.248633125233321</v>
       </c>
     </row>
     <row r="40">
@@ -1075,7 +1075,7 @@
         <v>2.382861024057354</v>
       </c>
       <c r="D40">
-        <v>-0.1374579045691964</v>
+        <v>-0.1374579045691997</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.1331321328381185</v>
+        <v>0.1331321328381177</v>
       </c>
       <c r="D41">
-        <v>-0.05484336538629848</v>
+        <v>-0.05484336538630035</v>
       </c>
     </row>
     <row r="42">
@@ -1111,7 +1111,7 @@
         <v>-2.232382955163989</v>
       </c>
       <c r="D42">
-        <v>0.4053314841213222</v>
+        <v>0.4053314841213218</v>
       </c>
     </row>
     <row r="43">
@@ -1129,7 +1129,7 @@
         <v>1.485656065696882</v>
       </c>
       <c r="D43">
-        <v>0.4548513520557838</v>
+        <v>0.4548513520557813</v>
       </c>
     </row>
     <row r="44">
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="C44">
-        <v>-1.589079934226805</v>
+        <v>-1.589079934226806</v>
       </c>
       <c r="D44">
-        <v>1.566899924412109E-05</v>
+        <v>1.566899924321241E-05</v>
       </c>
     </row>
     <row r="45">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.1937926101892735</v>
+        <v>0.1937926101892723</v>
       </c>
       <c r="D45">
-        <v>-0.6847087921201518</v>
+        <v>-0.6847087921201537</v>
       </c>
     </row>
     <row r="46">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="C46">
-        <v>1.894169268036832</v>
+        <v>1.894169268036831</v>
       </c>
       <c r="D46">
-        <v>0.1618645332054229</v>
+        <v>0.1618645332054197</v>
       </c>
     </row>
     <row r="47">
@@ -1201,7 +1201,7 @@
         <v>-1.2218887317131</v>
       </c>
       <c r="D47">
-        <v>-0.07832684551922103</v>
+        <v>-0.07832684551922209</v>
       </c>
     </row>
     <row r="48">
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="C48">
-        <v>1.086485378962956</v>
+        <v>1.086485378962955</v>
       </c>
       <c r="D48">
-        <v>-0.3859335880519657</v>
+        <v>-0.3859335880519682</v>
       </c>
     </row>
     <row r="49">
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.5117010307335299</v>
+        <v>0.5117010307335292</v>
       </c>
       <c r="D49">
-        <v>-0.08432151913382298</v>
+        <v>-0.08432151913382507</v>
       </c>
     </row>
     <row r="50">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.933140975216847</v>
+        <v>-0.9331409752168482</v>
       </c>
       <c r="D50">
-        <v>-0.6501417591935318</v>
+        <v>-0.650141759193533</v>
       </c>
     </row>
     <row r="51">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>0.1054875094116862</v>
+        <v>0.1054875094116855</v>
       </c>
       <c r="D51">
-        <v>-0.01880037407656921</v>
+        <v>-0.01880037407657107</v>
       </c>
     </row>
     <row r="52">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.07848060838322249</v>
+        <v>-0.07848060838322213</v>
       </c>
       <c r="D52">
-        <v>1.315639622490177</v>
+        <v>1.315639622490175</v>
       </c>
     </row>
     <row r="53">
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="C53">
-        <v>-1.688955097844375</v>
+        <v>-1.688955097844377</v>
       </c>
       <c r="D53">
-        <v>-0.7148828085902448</v>
+        <v>-0.7148828085902457</v>
       </c>
     </row>
     <row r="54">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.5303673985926166</v>
+        <v>0.5303673985926158</v>
       </c>
       <c r="D54">
-        <v>-0.04943281864877714</v>
+        <v>-0.04943281864877921</v>
       </c>
     </row>
     <row r="55">
@@ -1345,7 +1345,7 @@
         <v>-1.785900238163243</v>
       </c>
       <c r="D55">
-        <v>0.3138357066266128</v>
+        <v>0.3138357066266121</v>
       </c>
     </row>
     <row r="56">
@@ -1363,7 +1363,7 @@
         <v>-1.51208009504853</v>
       </c>
       <c r="D56">
-        <v>0.7873151087446663</v>
+        <v>0.7873151087446653</v>
       </c>
     </row>
     <row r="57">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="C57">
-        <v>-1.237246844692612</v>
+        <v>-1.237246844692613</v>
       </c>
       <c r="D57">
-        <v>0.2520598488596998</v>
+        <v>0.2520598488596988</v>
       </c>
     </row>
     <row r="58">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>-1.68601217024061</v>
+        <v>-1.686012170240612</v>
       </c>
       <c r="D58">
         <v>-1.157992593277081</v>
@@ -1417,7 +1417,7 @@
         <v>-2.041221031256511</v>
       </c>
       <c r="D59">
-        <v>0.9001534554199204</v>
+        <v>0.9001534554199199</v>
       </c>
     </row>
     <row r="60">
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.5024736339269051</v>
+        <v>0.502473633926904</v>
       </c>
       <c r="D60">
-        <v>-0.469209640653048</v>
+        <v>-0.4692096406530501</v>
       </c>
     </row>
     <row r="61">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="C61">
-        <v>-1.234064684015052</v>
+        <v>-1.234064684015053</v>
       </c>
       <c r="D61">
-        <v>0.3111698769916183</v>
+        <v>0.311169876991617</v>
       </c>
     </row>
     <row r="62">
@@ -1471,7 +1471,7 @@
         <v>-1.028097668338389</v>
       </c>
       <c r="D62">
-        <v>0.1702953934966654</v>
+        <v>0.1702953934966642</v>
       </c>
     </row>
     <row r="63">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="C63">
-        <v>-1.535547292340983</v>
+        <v>-1.535547292340984</v>
       </c>
       <c r="D63">
-        <v>-0.2449291791358373</v>
+        <v>-0.2449291791358383</v>
       </c>
     </row>
     <row r="64">
@@ -1507,7 +1507,7 @@
         <v>-1.638187814186608</v>
       </c>
       <c r="D64">
-        <v>0.4863007442767964</v>
+        <v>0.4863007442767954</v>
       </c>
     </row>
     <row r="65">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.4608710243713439</v>
+        <v>0.4608710243713426</v>
       </c>
       <c r="D65">
-        <v>-0.7429548137836359</v>
+        <v>-0.7429548137836379</v>
       </c>
     </row>
     <row r="66">
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.4096120152937888</v>
+        <v>0.4096120152937885</v>
       </c>
       <c r="D66">
-        <v>0.5932373266616874</v>
+        <v>0.5932373266616853</v>
       </c>
     </row>
     <row r="67">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.9823981809136958</v>
+        <v>0.9823981809136952</v>
       </c>
       <c r="D67">
-        <v>0.1190028323598879</v>
+        <v>0.1190028323598855</v>
       </c>
     </row>
     <row r="68">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>1.702136256783883</v>
+        <v>1.702136256783882</v>
       </c>
       <c r="D68">
-        <v>0.565100677151799</v>
+        <v>0.5651006771517961</v>
       </c>
     </row>
     <row r="69">
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.116133996942428</v>
+        <v>-0.1161339969424285</v>
       </c>
       <c r="D69">
-        <v>0.3095033433413078</v>
+        <v>0.3095033433413061</v>
       </c>
     </row>
     <row r="70">
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="C70">
-        <v>-1.211412940386421</v>
+        <v>-1.211412940386422</v>
       </c>
       <c r="D70">
-        <v>-0.198779062001266</v>
+        <v>-0.1987790620012669</v>
       </c>
     </row>
     <row r="71">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>-0.3958204273348096</v>
+        <v>-0.3958204273348108</v>
       </c>
       <c r="D71">
-        <v>-0.7497581212616056</v>
+        <v>-0.7497581212616071</v>
       </c>
     </row>
     <row r="72">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C72">
-        <v>2.230487238552071</v>
+        <v>2.230487238552072</v>
       </c>
       <c r="D72">
-        <v>2.097543667399595</v>
+        <v>2.097543667399592</v>
       </c>
     </row>
     <row r="73">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="C73">
-        <v>1.34304458008769</v>
+        <v>1.343044580087689</v>
       </c>
       <c r="D73">
-        <v>0.03828034346009287</v>
+        <v>0.03828034346009024</v>
       </c>
     </row>
     <row r="74">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.7700756400465348</v>
+        <v>0.7700756400465345</v>
       </c>
       <c r="D74">
-        <v>0.5567084817399713</v>
+        <v>0.5567084817399692</v>
       </c>
     </row>
     <row r="75">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>1.882809648686349</v>
+        <v>1.882809648686347</v>
       </c>
       <c r="D75">
-        <v>-0.977847376365561</v>
+        <v>-0.9778473763655638</v>
       </c>
     </row>
     <row r="76">
@@ -1723,7 +1723,7 @@
         <v>1.007137313494958</v>
       </c>
       <c r="D76">
-        <v>0.3726482591774571</v>
+        <v>0.3726482591774548</v>
       </c>
     </row>
     <row r="77">
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.04252822901638365</v>
+        <v>0.04252822901638242</v>
       </c>
       <c r="D77">
-        <v>-0.68622754187029</v>
+        <v>-0.6862275418702918</v>
       </c>
     </row>
     <row r="78">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C78">
-        <v>-1.893814631673849</v>
+        <v>-1.89381463167385</v>
       </c>
       <c r="D78">
-        <v>-0.3814907700774435</v>
+        <v>-0.3814907700774441</v>
       </c>
     </row>
     <row r="79">
@@ -1777,7 +1777,7 @@
         <v>1.200453284642075</v>
       </c>
       <c r="D79">
-        <v>0.635967597669005</v>
+        <v>0.6359675976690026</v>
       </c>
     </row>
     <row r="80">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.0183523145838325</v>
+        <v>0.01835231458383152</v>
       </c>
       <c r="D80">
-        <v>-0.3151477370545295</v>
+        <v>-0.3151477370545314</v>
       </c>
     </row>
     <row r="81">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="C81">
-        <v>0.5631041620721623</v>
+        <v>0.5631041620721619</v>
       </c>
       <c r="D81">
-        <v>0.3510624656636204</v>
+        <v>0.3510624656636183</v>
       </c>
     </row>
     <row r="82">
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="C82">
-        <v>-0.008893681761178345</v>
+        <v>-0.008893681761179273</v>
       </c>
       <c r="D82">
-        <v>-0.2536724429850492</v>
+        <v>-0.253672442985051</v>
       </c>
     </row>
     <row r="83">
@@ -1849,7 +1849,7 @@
         <v>-1.281104694064161</v>
       </c>
       <c r="D83">
-        <v>0.4910576189477989</v>
+        <v>0.4910576189477977</v>
       </c>
     </row>
     <row r="84">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="C84">
-        <v>-1.018688643507167</v>
+        <v>-1.018688643507168</v>
       </c>
       <c r="D84">
-        <v>-0.3417672448674299</v>
+        <v>-0.3417672448674312</v>
       </c>
     </row>
     <row r="85">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="C85">
-        <v>-1.22986154266327</v>
+        <v>-1.229861542663271</v>
       </c>
       <c r="D85">
-        <v>-0.1366178347898389</v>
+        <v>-0.1366178347898399</v>
       </c>
     </row>
     <row r="86">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="C86">
-        <v>0.1017430748952009</v>
+        <v>0.1017430748952004</v>
       </c>
       <c r="D86">
-        <v>0.2258340494051368</v>
+        <v>0.2258340494051349</v>
       </c>
     </row>
     <row r="87">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="C87">
-        <v>-0.2592696682893932</v>
+        <v>-0.259269668289394</v>
       </c>
       <c r="D87">
-        <v>-0.1872312090897344</v>
+        <v>-0.1872312090897361</v>
       </c>
     </row>
     <row r="88">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="C88">
-        <v>0.7462912859533</v>
+        <v>0.746291285953299</v>
       </c>
       <c r="D88">
-        <v>-0.3357492794702179</v>
+        <v>-0.3357492794702203</v>
       </c>
     </row>
     <row r="89">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.1585902655637408</v>
+        <v>-0.1585902655637419</v>
       </c>
       <c r="D89">
-        <v>-0.4019600167581308</v>
+        <v>-0.4019600167581325</v>
       </c>
     </row>
     <row r="90">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="C90">
-        <v>0.9063451044892378</v>
+        <v>0.906345104489237</v>
       </c>
       <c r="D90">
-        <v>-0.1308868485425752</v>
+        <v>-0.1308868485425775</v>
       </c>
     </row>
     <row r="91">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="C91">
-        <v>1.351840449279883</v>
+        <v>1.351840449279881</v>
       </c>
       <c r="D91">
-        <v>-0.9083773835066379</v>
+        <v>-0.9083773835066403</v>
       </c>
     </row>
     <row r="92">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="C92">
-        <v>2.208876301047288</v>
+        <v>2.208876301047287</v>
       </c>
       <c r="D92">
-        <v>-0.5476494417027044</v>
+        <v>-0.5476494417027074</v>
       </c>
     </row>
     <row r="93">
@@ -2029,7 +2029,7 @@
         <v>2.689647523416838</v>
       </c>
       <c r="D93">
-        <v>-0.3102225292512281</v>
+        <v>-0.3102225292512317</v>
       </c>
     </row>
     <row r="94">
@@ -2047,7 +2047,7 @@
         <v>1.243017557736244</v>
       </c>
       <c r="D94">
-        <v>0.4664702734551947</v>
+        <v>0.4664702734551921</v>
       </c>
     </row>
     <row r="95">
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="C95">
-        <v>2.887792241539022</v>
+        <v>2.88779224153902</v>
       </c>
       <c r="D95">
-        <v>-1.560272617531657</v>
+        <v>-1.560272617531661</v>
       </c>
     </row>
     <row r="96">
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.07906516636389326</v>
+        <v>0.07906516636389171</v>
       </c>
       <c r="D96">
-        <v>-0.874061103728639</v>
+        <v>-0.8740611037286408</v>
       </c>
     </row>
     <row r="97">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="C97">
-        <v>-2.032553079261013</v>
+        <v>-2.032553079261014</v>
       </c>
       <c r="D97">
-        <v>-0.1528916952271266</v>
+        <v>-0.1528916952271273</v>
       </c>
     </row>
     <row r="98">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="C98">
-        <v>1.109460502523076</v>
+        <v>1.109460502523074</v>
       </c>
       <c r="D98">
-        <v>-0.6586719230788111</v>
+        <v>-0.6586719230788134</v>
       </c>
     </row>
     <row r="99">
@@ -2137,7 +2137,7 @@
         <v>1.07330894297247</v>
       </c>
       <c r="D99">
-        <v>0.7255648296100901</v>
+        <v>0.7255648296100876</v>
       </c>
     </row>
     <row r="100">
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.9963774231762645</v>
+        <v>-0.9963774231762657</v>
       </c>
       <c r="D100">
-        <v>-0.5246799172965768</v>
+        <v>-0.5246799172965781</v>
       </c>
     </row>
     <row r="101">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="C101">
-        <v>1.222922163190474</v>
+        <v>1.222922163190473</v>
       </c>
       <c r="D101">
-        <v>-0.08991443202298353</v>
+        <v>-0.08991443202298599</v>
       </c>
     </row>
     <row r="102">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="C102">
-        <v>1.47722981198443</v>
+        <v>1.477229811984429</v>
       </c>
       <c r="D102">
-        <v>0.05439472005469301</v>
+        <v>0.05439472005469026</v>
       </c>
     </row>
     <row r="103">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="C103">
-        <v>-1.999257920007976</v>
+        <v>-1.999257920007977</v>
       </c>
       <c r="D103">
-        <v>-0.09818238556444159</v>
+        <v>-0.09818238556444214</v>
       </c>
     </row>
     <row r="104">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="C104">
-        <v>-0.1781709519005359</v>
+        <v>-0.1781709519005374</v>
       </c>
       <c r="D104">
-        <v>-0.8614076056406788</v>
+        <v>-0.8614076056406805</v>
       </c>
     </row>
     <row r="105">
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="C105">
-        <v>-0.6992959920833656</v>
+        <v>-0.6992959920833661</v>
       </c>
       <c r="D105">
-        <v>0.229959218353756</v>
+        <v>0.2299592183537547</v>
       </c>
     </row>
     <row r="106">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="C106">
-        <v>-0.8871747668952135</v>
+        <v>-0.8871747668952146</v>
       </c>
       <c r="D106">
-        <v>-0.222368599010943</v>
+        <v>-0.2223685990109443</v>
       </c>
     </row>
     <row r="107">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.03705124636907457</v>
+        <v>0.03705124636907359</v>
       </c>
       <c r="D107">
-        <v>-0.3474733038952691</v>
+        <v>-0.3474733038952709</v>
       </c>
     </row>
     <row r="108">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.9568966137032024</v>
+        <v>0.9568966137032017</v>
       </c>
       <c r="D108">
-        <v>0.01233355688881104</v>
+        <v>0.01233355688880866</v>
       </c>
     </row>
     <row r="109">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.07900418800369102</v>
+        <v>-0.07900418800369247</v>
       </c>
       <c r="D109">
-        <v>-0.8528179434894809</v>
+        <v>-0.8528179434894827</v>
       </c>
     </row>
     <row r="110">
@@ -2335,7 +2335,7 @@
         <v>1.692863818466118</v>
       </c>
       <c r="D110">
-        <v>0.6119374723889905</v>
+        <v>0.6119374723889877</v>
       </c>
     </row>
     <row r="111">
@@ -2353,7 +2353,7 @@
         <v>-1.111063164485824</v>
       </c>
       <c r="D111">
-        <v>0.329448632075383</v>
+        <v>0.3294486320753819</v>
       </c>
     </row>
     <row r="112">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.1651022391835722</v>
+        <v>0.1651022391835718</v>
       </c>
       <c r="D112">
-        <v>0.321320888827081</v>
+        <v>0.3213208888270792</v>
       </c>
     </row>
     <row r="113">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.3260951179176248</v>
+        <v>-0.3260951179176254</v>
       </c>
       <c r="D113">
-        <v>0.06776876800836848</v>
+        <v>0.06776876800836687</v>
       </c>
     </row>
     <row r="114">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="C114">
-        <v>0.1890158114889776</v>
+        <v>0.1890158114889771</v>
       </c>
       <c r="D114">
-        <v>0.2655850402751683</v>
+        <v>0.2655850402751665</v>
       </c>
     </row>
     <row r="115">
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="C115">
-        <v>0.1830025218696298</v>
+        <v>0.1830025218696288</v>
       </c>
       <c r="D115">
-        <v>-0.3156088950877856</v>
+        <v>-0.3156088950877874</v>
       </c>
     </row>
     <row r="116">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="C116">
-        <v>-0.8495647564236311</v>
+        <v>-0.8495647564236317</v>
       </c>
       <c r="D116">
-        <v>0.02470731560659089</v>
+        <v>0.02470731560658962</v>
       </c>
     </row>
     <row r="117">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="C117">
-        <v>3.642724211932077</v>
+        <v>3.642724211932076</v>
       </c>
       <c r="D117">
-        <v>-0.04199906964826446</v>
+        <v>-0.04199906964826861</v>
       </c>
     </row>
     <row r="118">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="C118">
-        <v>0.3999316147222406</v>
+        <v>0.3999316147222394</v>
       </c>
       <c r="D118">
-        <v>-0.6622891552547532</v>
+        <v>-0.6622891552547552</v>
       </c>
     </row>
     <row r="119">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="C119">
-        <v>-0.6154168024362912</v>
+        <v>-0.6154168024362914</v>
       </c>
       <c r="D119">
-        <v>0.5433138440564597</v>
+        <v>0.5433138440564583</v>
       </c>
     </row>
     <row r="120">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.2395540415152624</v>
+        <v>-0.2395540415152635</v>
       </c>
       <c r="D120">
-        <v>-0.3675158923874265</v>
+        <v>-0.3675158923874282</v>
       </c>
     </row>
     <row r="121">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="C121">
-        <v>0.0510216886408565</v>
+        <v>0.05102168864085624</v>
       </c>
       <c r="D121">
-        <v>0.533407359629972</v>
+        <v>0.5334073596299701</v>
       </c>
     </row>
     <row r="122">
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.2523141965649053</v>
+        <v>-0.2523141965649064</v>
       </c>
       <c r="D122">
-        <v>-0.4521360851048877</v>
+        <v>-0.4521360851048893</v>
       </c>
     </row>
     <row r="123">
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.7546082290100903</v>
+        <v>0.7546082290100899</v>
       </c>
       <c r="D123">
-        <v>0.4563507571557294</v>
+        <v>0.4563507571557272</v>
       </c>
     </row>
     <row r="124">
@@ -2587,7 +2587,7 @@
         <v>-1.318902015174164</v>
       </c>
       <c r="D124">
-        <v>0.6313757606051325</v>
+        <v>0.6313757606051316</v>
       </c>
     </row>
     <row r="125">
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="C125">
-        <v>-0.2228320327497476</v>
+        <v>-0.2228320327497481</v>
       </c>
       <c r="D125">
-        <v>0.3835320264847611</v>
+        <v>0.3835320264847595</v>
       </c>
     </row>
     <row r="126">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="C126">
-        <v>-0.4226911160922976</v>
+        <v>-0.4226911160922985</v>
       </c>
       <c r="D126">
-        <v>-0.216749655523911</v>
+        <v>-0.2167496555239126</v>
       </c>
     </row>
   </sheetData>
